--- a/education_forms/046_remote_teaching_tools_faculty_inquiry_form--education_forms.xlsx
+++ b/education_forms/046_remote_teaching_tools_faculty_inquiry_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_1</t>
+          <t>remote_teaching_tools</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What kind of remote teaching technology have you used</t>
+          <t>What kind of remote teaching technology have you used?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_2</t>
+          <t>teaching_technology_helpfulness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What was most helpful in terms of remote teaching technology</t>
+          <t>What was most helpful in terms of remote teaching technology?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_3</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How would you rate your overall satisfaction with remote teaching technology</t>
+          <t>How would you rate your overall satisfaction with remote teaching technology?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_4</t>
+          <t>support_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What kind of support would you like to see</t>
+          <t>What kind of support would you like to see for remote teaching technology?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_5</t>
+          <t>usage_count</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How many times have you used remote teaching technology</t>
+          <t>How many times have you used remote teaching technology?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_6</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Do you have any suggestions</t>
+          <t>Do you have any suggestions for improving remote teaching technology?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_7</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you have any other comments</t>
+          <t>Do you have any other comments?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_8</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you have any other comments</t>
+          <t>Have you encountered any technical issues with remote teaching technology?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_9</t>
+          <t>essential_features</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Do you have any other comments</t>
+          <t>What features do you think are essential for effective remote teaching?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_10</t>
+          <t>adequate_support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Do you have any other comments</t>
+          <t>Have you received adequate support for remote teaching technology?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_11</t>
+          <t>other_tools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Do you have any other comments</t>
+          <t>What other tools or platforms have you used for remote teaching?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_1_choices</t>
+          <t>remote_teaching_tools_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_1_choices</t>
+          <t>remote_teaching_tools_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_1_choices</t>
+          <t>remote_teaching_tools_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,136 +855,238 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_1_choices</t>
+          <t>teaching_technology_helpfulness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>sufficient</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sufficient</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_2_choices</t>
+          <t>teaching_technology_helpfulness_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sufficient</t>
+          <t>not_sufficient</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sufficient</t>
+          <t>Not Sufficient</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_2_choices</t>
+          <t>teaching_technology_helpfulness_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_sufficient</t>
+          <t>no_opinion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not Sufficient</t>
+          <t>No opinion</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_2_choices</t>
+          <t>support_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no_opinion</t>
+          <t>technical_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No opinion</t>
+          <t>Technical Support</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_4_choices</t>
+          <t>support_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>technical_support</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technical Support</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_4_choices</t>
+          <t>support_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_4_choices</t>
+          <t>essential_features_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>video_conferencing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Video conferencing</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>remote_teaching_tools_faculty_inquiry_form_4_choices</t>
+          <t>essential_features_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>audio_conferencing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Audio conferencing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>essential_features_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>chat_or_messaging</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chat or messaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>essential_features_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>polling_or_quizzing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Polling or quizzing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>other_tools_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>other_tools_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>zoom</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Zoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>other_tools_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>google_meet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Google Meet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>other_tools_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>skype</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Skype</t>
         </is>
       </c>
     </row>
